--- a/MainTop/22.09.2026 МПЕ/Москва_p1.xlsx
+++ b/MainTop/22.09.2026 МПЕ/Москва_p1.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L44"/>
+  <dimension ref="A1:L24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1766,1126 +1766,6 @@
         <v>12</v>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Термобирки Дмитрий</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Дмитрий</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>12</v>
-      </c>
-      <c r="D25" t="n">
-        <v>1296053164</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Дефицитный</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Сортируемый товар</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>4_имена</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>22.09.2026 МПЕ</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>Термобирки Вероника</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Вероника</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>12</v>
-      </c>
-      <c r="D26" t="n">
-        <v>1302408998</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Дефицитный</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Сортируемый товар</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>4_имена</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>22.09.2026 МПЕ</t>
-        </is>
-      </c>
-      <c r="L26" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>Термобирки Влад</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Термобирки Влад</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>12</v>
-      </c>
-      <c r="D27" t="n">
-        <v>2365502926</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Дефицитный</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Сортируемый товар</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>4_имена</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>22.09.2026 МПЕ</t>
-        </is>
-      </c>
-      <c r="L27" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>Термобирки Мирослава</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Мирослава</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>11</v>
-      </c>
-      <c r="D28" t="n">
-        <v>1302409296</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Дефицитный</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Сортируемый товар</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>4_имена</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>22.09.2026 МПЕ</t>
-        </is>
-      </c>
-      <c r="L28" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Термобирки Ксения</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Ксения</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>11</v>
-      </c>
-      <c r="D29" t="n">
-        <v>1302409277</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Дефицитный</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Сортируемый товар</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>4_имена</t>
-        </is>
-      </c>
-      <c r="K29" t="inlineStr">
-        <is>
-          <t>22.09.2026 МПЕ</t>
-        </is>
-      </c>
-      <c r="L29" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Термобирки Алиса</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Алиса</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>11</v>
-      </c>
-      <c r="D30" t="n">
-        <v>1302409496</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Дефицитный</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Сортируемый товар</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>4_имена</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>22.09.2026 МПЕ</t>
-        </is>
-      </c>
-      <c r="L30" t="n">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Термобирки Ульяна</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Термобирки Ульяна</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>10</v>
-      </c>
-      <c r="D31" t="n">
-        <v>2366379751</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Дефицитный</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Сортируемый товар</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>4_имена</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>22.09.2026 МПЕ</t>
-        </is>
-      </c>
-      <c r="L31" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Термобирки Иван</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Марк</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>10</v>
-      </c>
-      <c r="D32" t="n">
-        <v>1296050885</v>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Дефицитный</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Сортируемый товар</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>4_имена</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>22.09.2026 МПЕ</t>
-        </is>
-      </c>
-      <c r="L32" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>Термобирки Мария</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Мария</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>10</v>
-      </c>
-      <c r="D33" t="n">
-        <v>1302410399</v>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Дефицитный</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>Сортируемый товар</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>4_имена</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>22.09.2026 МПЕ</t>
-        </is>
-      </c>
-      <c r="L33" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>Термобирки Виктория</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Виктория</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>10</v>
-      </c>
-      <c r="D34" t="n">
-        <v>1302407457</v>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Дефицитный</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Сортируемый товар</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>4_имена</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>22.09.2026 МПЕ</t>
-        </is>
-      </c>
-      <c r="L34" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>Термобирки Василиса</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Василиса</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>10</v>
-      </c>
-      <c r="D35" t="n">
-        <v>1302409288</v>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Дефицитный</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>Сортируемый товар</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>4_имена</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>22.09.2026 МПЕ</t>
-        </is>
-      </c>
-      <c r="L35" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Термобирки Эмилия</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Эмилия</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>9</v>
-      </c>
-      <c r="D36" t="n">
-        <v>1302409040</v>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Дефицитный</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Сортируемый товар</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>4_имена</t>
-        </is>
-      </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>22.09.2026 МПЕ</t>
-        </is>
-      </c>
-      <c r="L36" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Термобирки Макар</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Макар</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>9</v>
-      </c>
-      <c r="D37" t="n">
-        <v>1296068268</v>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Дефицитный</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>Сортируемый товар</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>4_имена</t>
-        </is>
-      </c>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>22.09.2026 МПЕ</t>
-        </is>
-      </c>
-      <c r="L37" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Термобирки Кира</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Кира</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>9</v>
-      </c>
-      <c r="D38" t="n">
-        <v>1302409262</v>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Дефицитный</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Сортируемый товар</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>4_имена</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>22.09.2026 МПЕ</t>
-        </is>
-      </c>
-      <c r="L38" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>Термобирки Богдан</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Богдан</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>9</v>
-      </c>
-      <c r="D39" t="n">
-        <v>1296068312</v>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Дефицитный</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>Сортируемый товар</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>4_имена</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>22.09.2026 МПЕ</t>
-        </is>
-      </c>
-      <c r="L39" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>Термобирки Анна</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Анна</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>9</v>
-      </c>
-      <c r="D40" t="n">
-        <v>1302411737</v>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Дефицитный</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Сортируемый товар</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="J40" t="inlineStr">
-        <is>
-          <t>4_имена</t>
-        </is>
-      </c>
-      <c r="K40" t="inlineStr">
-        <is>
-          <t>22.09.2026 МПЕ</t>
-        </is>
-      </c>
-      <c r="L40" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Термобирки Алексей</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Алексей</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>9</v>
-      </c>
-      <c r="D41" t="n">
-        <v>1296065057</v>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Дефицитный</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Сортируемый товар</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="J41" t="inlineStr">
-        <is>
-          <t>4_имена</t>
-        </is>
-      </c>
-      <c r="K41" t="inlineStr">
-        <is>
-          <t>22.09.2026 МПЕ</t>
-        </is>
-      </c>
-      <c r="L41" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Термобирки Аделина</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Аделина</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>9</v>
-      </c>
-      <c r="D42" t="n">
-        <v>1302409334</v>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Дефицитный</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>Сортируемый товар</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>4_имена</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>22.09.2026 МПЕ</t>
-        </is>
-      </c>
-      <c r="L42" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Термобирки Николай</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Термобирки Николай</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>8</v>
-      </c>
-      <c r="D43" t="n">
-        <v>2365501207</v>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Дефицитный</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>Сортируемый товар</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>4_имена</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>22.09.2026 МПЕ</t>
-        </is>
-      </c>
-      <c r="L43" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Термобирки Есения</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Термобирки именные для одежды и маркировки детской одежды в детский сад, именные наклейки, термостикеры, стикеры, бирки. Есения</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>8</v>
-      </c>
-      <c r="D44" t="n">
-        <v>1302409123</v>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Дефицитный</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Сортируемый товар</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>Нет</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>4_имена</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>22.09.2026 МПЕ</t>
-        </is>
-      </c>
-      <c r="L44" t="n">
-        <v>8</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
